--- a/2.xlsx
+++ b/2.xlsx
@@ -23,27 +23,33 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
-  <si>
-    <t>Результат1 (0,006 мс., строк: 1)</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+  <si>
+    <t>Результат1 (0,007 мс., строк: 1)</t>
   </si>
   <si>
     <t>Период</t>
   </si>
   <si>
+    <t>Организация</t>
+  </si>
+  <si>
     <t>СчетДоверительногоУправления</t>
   </si>
   <si>
-    <t>НастройкаГрафика</t>
+    <t>ВестиЕдиныйБухгалтерскийУчет</t>
   </si>
   <si>
     <t>18.11.2025 0:00:00</t>
   </si>
   <si>
+    <t>РЕГИОН ЭсМ</t>
+  </si>
+  <si>
     <t>Файзутдинов Илдар Шафигуллович</t>
   </si>
   <si>
-    <t>Ежедневно по рабочим и в конце месяца</t>
+    <t>Нет</t>
   </si>
 </sst>
 </file>
@@ -53,7 +59,7 @@
   <numFmts count="1">
     <numFmt numFmtId="50" formatCode=""/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Arial"/>
       <sz val="8"/>
@@ -97,6 +103,17 @@
       <i val="false"/>
       <strike val="false"/>
       <color rgb="000000"/>
+      <sz val="8"/>
+      <u val="none"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <family val="2"/>
+      <b val="false"/>
+      <i val="false"/>
+      <strike val="false"/>
+      <color rgb="2F4F4F"/>
       <sz val="8"/>
       <u val="none"/>
     </font>
@@ -142,7 +159,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0"/>
     <xf numFmtId="0" fontId="0" applyAlignment="true">
       <alignment horizontal="left"/>
@@ -157,6 +174,9 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="4" borderId="1" applyFont="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" borderId="1" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -178,15 +198,17 @@
     <outlinePr summaryBelow="false" summaryRight="false"/>
     <pageSetUpPr autoPageBreaks="false" fitToPage="false"/>
   </sheetPr>
-  <dimension ref="F4"/>
+  <dimension ref="H4"/>
   <sheetFormatPr defaultColWidth="10.5" customHeight="true" defaultRowHeight="11.429"/>
   <cols>
     <col min="1" max="1" width="10.5" style="1" customWidth="true"/>
     <col min="2" max="2" width="10.5" style="1" customWidth="true"/>
     <col min="3" max="3" width="1.16796875" style="1" customWidth="true"/>
     <col min="4" max="4" width="9.33203125" style="1" customWidth="true"/>
-    <col min="5" max="5" width="25.66796875" style="1" customWidth="true"/>
-    <col min="6" max="6" width="43.16796875" style="1" customWidth="true"/>
+    <col min="5" max="5" width="2.33203125" style="1" customWidth="true"/>
+    <col min="6" max="6" width="8.16796875" style="1" customWidth="true"/>
+    <col min="7" max="7" width="26.83203125" style="1" customWidth="true"/>
+    <col min="8" max="8" width="5.83203125" style="1" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1" ht="11" customHeight="true"/>
@@ -208,27 +230,37 @@
       <c r="F3" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="G3" s="3" t="e"/>
+      <c r="H3" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="4" ht="11" customHeight="true" s="1" customFormat="true" outlineLevel="1">
       <c r="A4" s="4" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B4" s="4" t="e"/>
       <c r="C4" s="4" t="e"/>
       <c r="D4" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E4" s="5" t="e"/>
       <c r="F4" s="5" t="s">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="G4" s="5" t="e"/>
+      <c r="H4" s="6" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="6">
     <mergeCell ref="A3:C3"/>
     <mergeCell ref="D3:E3"/>
+    <mergeCell ref="F3:G3"/>
     <mergeCell ref="A4:C4"/>
     <mergeCell ref="D4:E4"/>
+    <mergeCell ref="F4:G4"/>
   </mergeCells>
   <pageMargins left="0.393700787401574803149606299" top="0.393700787401574803149606299" right="0.393700787401574803149606299" bottom="0.393700787401574803149606299" header="0" footer="0"/>
   <pageSetup blackAndWhite="false" scale="100" pageOrder="overThenDown" orientation="portrait" paperSize="9"/>
